--- a/MomijiStore_OS/01_InventoryManagement/SourceData/全体在庫サマリー_v1.0.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/全体在庫サマリー_v1.0.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -510,10 +510,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>集計日時: 2026/08/03 15:39　（データ元: 楽天在庫リスト_import.xlsx「楽天単独在庫」シート / Amazon在庫リスト_import.xlsx）</t>
-        </is>
-      </c>
-    </row>
+          <t>集計日時: 2026/09/20 23:07　（データ元: 楽天在庫リスト_import.xlsx「楽天単独在庫」シート / Amazon在庫リスト_import.xlsx）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -553,20 +554,20 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3870</v>
+        <v>3371</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8274577</v>
+        <v>7024963</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Amazon共有(-a)398行は除外済み</t>
+          <t>Amazon共有(-a 367行＋承認済み例外 2行)は除外済み。在庫金額はリストの単価×在庫数。単価0(在庫&gt;0) 13行</t>
         </is>
       </c>
     </row>
@@ -577,18 +578,18 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>36906</v>
+        <v>13952</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -597,16 +598,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>9057</v>
+        <v>9497</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12285587</v>
+        <v>12852158</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -642,6 +643,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
@@ -677,6 +679,50 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>■ 注記(自動更新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>・基準日時 — 楽天: 資料基準日時 2026-09-16 08:11:29 ／ 取込実行日時 2026-09-20 21:23:12。 Amazon: 取得日時 2026-09-16 08:15 ／ 在庫基準日時 未取得(取得日時を基準日時として扱わない)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>・この表は共有在庫込み・原価未登録ありの「掲載分集計」であり、全社の確定在庫数量・確定評価額ではない(ChatGPT 2026-09-19)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>・楽天の在庫ツール(原価マスター参照・共有在庫込み): 総在庫金額 12,621,422 / 総在庫数量 5,911 / 原価未登録 59(集計 2026/09/20 21:23:15)。参考値。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>・最新CSVに無い商品(楽天94件・旧469個・参考額1,286,025円は削除記録CSV、Amazon40件・旧186個・参考額246,577円は別シート「未掲載_未確認」)は本表に含めない。現在在庫は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>・単価未入力 = 在庫&gt;0 で単価が空欄の行数(金額に入れない)。単価0 = 0円という値(金額0で計上・備考に件数)。在庫数の空欄=未入力・非数値=データ異常は数量・金額から除外し備考に件数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
